--- a/CG.xlsx
+++ b/CG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentJackOMahoney(\Desktop\CG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AA4E366-E339-4BC7-8F17-B07226CCD79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BEF1C2-7663-4F11-9F37-923EF4C13A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6060" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{E20A583D-468C-4979-B00F-9B1377DA2B19}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E20A583D-468C-4979-B00F-9B1377DA2B19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>X</t>
   </si>
@@ -50,7 +50,10 @@
     <t>z</t>
   </si>
   <si>
-    <t>Face Index List</t>
+    <t>Back Face Index List</t>
+  </si>
+  <si>
+    <t>Front Face Index List</t>
   </si>
 </sst>
 </file>
@@ -299,10 +302,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -653,47 +655,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F82094-B8A6-4AD9-9CFC-5B8CF8CA2C1B}">
-  <dimension ref="A1:BZ29"/>
+  <dimension ref="B1:BZ29"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="28" max="28" width="2.5" style="2"/>
     <col min="29" max="30" width="2.875" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="2.875" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="5" customWidth="1"/>
     <col min="48" max="48" width="2.875" bestFit="1" customWidth="1"/>
     <col min="49" max="50" width="4.5" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="2.5" customWidth="1"/>
-    <col min="59" max="60" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78">
-      <c r="A1" s="2"/>
+    <row r="1" spans="2:78">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:78">
-      <c r="B2" s="2"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="2:78">
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:78">
-      <c r="B3" s="2"/>
+    <row r="3" spans="2:78">
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:78">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+    <row r="4" spans="2:78">
       <c r="D4" s="1"/>
-      <c r="BV4" s="14"/>
-      <c r="BW4" s="13"/>
-      <c r="BX4" s="4"/>
-      <c r="BY4" s="13"/>
-      <c r="BZ4" s="15"/>
-    </row>
-    <row r="5" spans="1:78">
-      <c r="B5" s="7"/>
+      <c r="BV4" s="13"/>
+      <c r="BW4" s="12"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="12"/>
+      <c r="BZ4" s="14"/>
+    </row>
+    <row r="5" spans="2:78">
+      <c r="B5" s="6"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="AO5" t="s">
@@ -712,12 +708,11 @@
         <v>2</v>
       </c>
       <c r="BF5" t="s">
-        <v>3</v>
-      </c>
-      <c r="BV5" s="2"/>
-      <c r="BX5" s="16"/>
-    </row>
-    <row r="6" spans="1:78">
+        <v>4</v>
+      </c>
+      <c r="BX5" s="15"/>
+    </row>
+    <row r="6" spans="2:78">
       <c r="AN6">
         <v>0</v>
       </c>
@@ -739,10 +734,9 @@
       <c r="AY6">
         <v>1</v>
       </c>
-      <c r="BV6" s="2"/>
-      <c r="BX6" s="16"/>
-    </row>
-    <row r="7" spans="1:78">
+      <c r="BX6" s="15"/>
+    </row>
+    <row r="7" spans="2:78">
       <c r="AD7">
         <v>0</v>
       </c>
@@ -782,26 +776,24 @@
       <c r="BI7">
         <v>5</v>
       </c>
-      <c r="BV7" s="2"/>
-      <c r="BW7" s="2"/>
-      <c r="BX7" s="16"/>
-    </row>
-    <row r="8" spans="1:78">
-      <c r="S8" s="14"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="15"/>
+      <c r="BX7" s="15"/>
+    </row>
+    <row r="8" spans="2:78">
+      <c r="S8" s="13"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="14"/>
       <c r="AC8">
         <v>2</v>
       </c>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="5"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="4"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1">
         <v>4</v>
       </c>
-      <c r="AH8" s="12"/>
+      <c r="AH8" s="11"/>
       <c r="AI8">
         <v>5</v>
       </c>
@@ -838,14 +830,12 @@
       <c r="BI8">
         <v>1</v>
       </c>
-      <c r="BV8" s="18"/>
-      <c r="BW8" s="13"/>
-      <c r="BX8" s="17"/>
-    </row>
-    <row r="9" spans="1:78">
-      <c r="S9" s="2"/>
-      <c r="U9" s="16"/>
-      <c r="AD9" s="2"/>
+      <c r="BV8" s="17"/>
+      <c r="BW8" s="12"/>
+      <c r="BX8" s="16"/>
+    </row>
+    <row r="9" spans="2:78">
+      <c r="U9" s="15"/>
       <c r="AE9">
         <v>3</v>
       </c>
@@ -887,10 +877,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:78">
-      <c r="S10" s="2"/>
-      <c r="U10" s="16"/>
-      <c r="AD10" s="2"/>
+    <row r="10" spans="2:78">
+      <c r="U10" s="15"/>
       <c r="AF10" s="1"/>
       <c r="AN10">
         <v>4</v>
@@ -926,15 +914,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:78">
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="16"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2">
+    <row r="11" spans="2:78">
+      <c r="U11" s="15"/>
+      <c r="AE11">
         <v>7</v>
       </c>
-      <c r="AF11" s="9"/>
+      <c r="AF11" s="8"/>
       <c r="AN11">
         <v>5</v>
       </c>
@@ -969,16 +954,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:78">
-      <c r="S12" s="18"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="17"/>
+    <row r="12" spans="2:78">
+      <c r="S12" s="17"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="16"/>
       <c r="AC12">
         <v>11</v>
       </c>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="11"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="10"/>
       <c r="AG12">
         <v>8</v>
       </c>
@@ -1016,7 +1001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:78">
+    <row r="13" spans="2:78">
       <c r="AD13">
         <v>10</v>
       </c>
@@ -1045,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:78">
+    <row r="14" spans="2:78">
       <c r="AN14">
         <v>8</v>
       </c>
@@ -1067,8 +1052,11 @@
       <c r="AY14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:78">
+      <c r="BF14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:78">
       <c r="AN15">
         <v>9</v>
       </c>
@@ -1090,8 +1078,20 @@
       <c r="AY15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:78">
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>10</v>
+      </c>
+      <c r="BH15">
+        <v>9</v>
+      </c>
+      <c r="BI15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:78">
       <c r="AN16">
         <v>10</v>
       </c>
@@ -1113,8 +1113,20 @@
       <c r="AY16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="40:51">
+      <c r="BF16">
+        <v>1</v>
+      </c>
+      <c r="BG16">
+        <v>10</v>
+      </c>
+      <c r="BH16">
+        <v>6</v>
+      </c>
+      <c r="BI16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="40:61">
       <c r="AN17">
         <v>11</v>
       </c>
@@ -1136,8 +1148,20 @@
       <c r="AY17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="40:51">
+      <c r="BF17">
+        <v>2</v>
+      </c>
+      <c r="BG17">
+        <v>8</v>
+      </c>
+      <c r="BH17">
+        <v>5</v>
+      </c>
+      <c r="BI17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="40:61">
       <c r="AV18">
         <v>12</v>
       </c>
@@ -1150,8 +1174,20 @@
       <c r="AY18">
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="40:51">
+      <c r="BF18">
+        <v>3</v>
+      </c>
+      <c r="BG18">
+        <v>8</v>
+      </c>
+      <c r="BH18">
+        <v>3</v>
+      </c>
+      <c r="BI18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="40:61">
       <c r="AV19">
         <v>13</v>
       </c>
@@ -1164,8 +1200,20 @@
       <c r="AY19">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="40:51">
+      <c r="BF19">
+        <v>4</v>
+      </c>
+      <c r="BG19">
+        <v>4</v>
+      </c>
+      <c r="BH19">
+        <v>2</v>
+      </c>
+      <c r="BI19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="40:61">
       <c r="AV20">
         <v>14</v>
       </c>
@@ -1178,8 +1226,20 @@
       <c r="AY20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="40:51">
+      <c r="BF20">
+        <v>5</v>
+      </c>
+      <c r="BG20">
+        <v>4</v>
+      </c>
+      <c r="BH20">
+        <v>1</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="40:61">
       <c r="AV21">
         <v>15</v>
       </c>
@@ -1193,7 +1253,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="40:51">
+    <row r="22" spans="40:61">
       <c r="AV22">
         <v>16</v>
       </c>
@@ -1207,7 +1267,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="40:51">
+    <row r="23" spans="40:61">
       <c r="AV23">
         <v>17</v>
       </c>
@@ -1221,7 +1281,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="40:51">
+    <row r="24" spans="40:61">
       <c r="AV24">
         <v>18</v>
       </c>
@@ -1235,7 +1295,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="40:51">
+    <row r="25" spans="40:61">
       <c r="AV25">
         <v>19</v>
       </c>
@@ -1249,7 +1309,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="40:51">
+    <row r="26" spans="40:61">
       <c r="AV26">
         <v>20</v>
       </c>
@@ -1263,7 +1323,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="40:51">
+    <row r="27" spans="40:61">
       <c r="AV27">
         <v>21</v>
       </c>
@@ -1277,7 +1337,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="40:51">
+    <row r="28" spans="40:61">
       <c r="AV28">
         <v>22</v>
       </c>
@@ -1291,7 +1351,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="40:51">
+    <row r="29" spans="40:61">
       <c r="AV29">
         <v>23</v>
       </c>

--- a/CG.xlsx
+++ b/CG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentJackOMahoney(\Desktop\CG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BEF1C2-7663-4F11-9F37-923EF4C13A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4A9039-3890-4A2C-B3C3-F73DF2C513E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E20A583D-468C-4979-B00F-9B1377DA2B19}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,31 +656,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F82094-B8A6-4AD9-9CFC-5B8CF8CA2C1B}">
   <dimension ref="B1:BZ29"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="29" max="30" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="5" customWidth="1"/>
-    <col min="48" max="48" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="2.5" customWidth="1"/>
-    <col min="59" max="61" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="2.42578125" customWidth="1"/>
+    <col min="59" max="61" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:78">
+    <row r="1" spans="2:78" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="2:78">
+    <row r="2" spans="2:78" x14ac:dyDescent="0.25">
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="2:78">
+    <row r="3" spans="2:78" x14ac:dyDescent="0.25">
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="2:78">
+    <row r="4" spans="2:78" x14ac:dyDescent="0.25">
       <c r="D4" s="1"/>
       <c r="BV4" s="13"/>
       <c r="BW4" s="12"/>
@@ -688,7 +688,7 @@
       <c r="BY4" s="12"/>
       <c r="BZ4" s="14"/>
     </row>
-    <row r="5" spans="2:78">
+    <row r="5" spans="2:78" x14ac:dyDescent="0.25">
       <c r="B5" s="6"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -712,7 +712,7 @@
       </c>
       <c r="BX5" s="15"/>
     </row>
-    <row r="6" spans="2:78">
+    <row r="6" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AN6">
         <v>0</v>
       </c>
@@ -736,7 +736,7 @@
       </c>
       <c r="BX6" s="15"/>
     </row>
-    <row r="7" spans="2:78">
+    <row r="7" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AD7">
         <v>0</v>
       </c>
@@ -778,7 +778,7 @@
       </c>
       <c r="BX7" s="15"/>
     </row>
-    <row r="8" spans="2:78">
+    <row r="8" spans="2:78" x14ac:dyDescent="0.25">
       <c r="S8" s="13"/>
       <c r="T8" s="12"/>
       <c r="U8" s="3"/>
@@ -834,7 +834,7 @@
       <c r="BW8" s="12"/>
       <c r="BX8" s="16"/>
     </row>
-    <row r="9" spans="2:78">
+    <row r="9" spans="2:78" x14ac:dyDescent="0.25">
       <c r="U9" s="15"/>
       <c r="AE9">
         <v>3</v>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:78">
+    <row r="10" spans="2:78" x14ac:dyDescent="0.25">
       <c r="U10" s="15"/>
       <c r="AF10" s="1"/>
       <c r="AN10">
@@ -914,7 +914,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:78">
+    <row r="11" spans="2:78" x14ac:dyDescent="0.25">
       <c r="U11" s="15"/>
       <c r="AE11">
         <v>7</v>
@@ -954,7 +954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:78">
+    <row r="12" spans="2:78" x14ac:dyDescent="0.25">
       <c r="S12" s="17"/>
       <c r="T12" s="12"/>
       <c r="U12" s="16"/>
@@ -1001,7 +1001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:78">
+    <row r="13" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AD13">
         <v>10</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:78">
+    <row r="14" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AN14">
         <v>8</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:78">
+    <row r="15" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AN15">
         <v>9</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:78">
+    <row r="16" spans="2:78" x14ac:dyDescent="0.25">
       <c r="AN16">
         <v>10</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="40:61">
+    <row r="17" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AN17">
         <v>11</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="40:61">
+    <row r="18" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV18">
         <v>12</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="40:61">
+    <row r="19" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV19">
         <v>13</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="40:61">
+    <row r="20" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV20">
         <v>14</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="40:61">
+    <row r="21" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV21">
         <v>15</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="40:61">
+    <row r="22" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV22">
         <v>16</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="40:61">
+    <row r="23" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV23">
         <v>17</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="40:61">
+    <row r="24" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV24">
         <v>18</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="40:61">
+    <row r="25" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV25">
         <v>19</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="40:61">
+    <row r="26" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV26">
         <v>20</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="40:61">
+    <row r="27" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV27">
         <v>21</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="40:61">
+    <row r="28" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV28">
         <v>22</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="40:61">
+    <row r="29" spans="40:61" x14ac:dyDescent="0.25">
       <c r="AV29">
         <v>23</v>
       </c>

--- a/CG.xlsx
+++ b/CG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentJackOMahoney(\Desktop\CG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4A9039-3890-4A2C-B3C3-F73DF2C513E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F642D14D-771A-469A-BBE9-D85EB049B6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E20A583D-468C-4979-B00F-9B1377DA2B19}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,7 +77,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -298,11 +298,98 @@
         <color auto="1"/>
       </diagonal>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -321,6 +408,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,42 +750,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F82094-B8A6-4AD9-9CFC-5B8CF8CA2C1B}">
   <dimension ref="B1:BZ29"/>
-  <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="29" max="30" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.875" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="5" customWidth="1"/>
-    <col min="48" max="48" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="2.42578125" customWidth="1"/>
-    <col min="59" max="61" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="4.375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="2.375" customWidth="1"/>
+    <col min="59" max="61" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:78">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:78">
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:78">
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:78" ht="15" thickBot="1">
       <c r="D4" s="1"/>
+      <c r="Z4">
+        <v>15</v>
+      </c>
+      <c r="AB4">
+        <v>3</v>
+      </c>
       <c r="BV4" s="13"/>
       <c r="BW4" s="12"/>
       <c r="BX4" s="3"/>
       <c r="BY4" s="12"/>
       <c r="BZ4" s="14"/>
     </row>
-    <row r="5" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:78" ht="15.75" thickTop="1" thickBot="1">
       <c r="B5" s="6"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
+      <c r="AA5" s="8"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="20"/>
       <c r="AO5" t="s">
         <v>0</v>
       </c>
@@ -712,7 +819,14 @@
       </c>
       <c r="BX5" s="15"/>
     </row>
-    <row r="6" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:78" ht="15" thickTop="1">
+      <c r="AA6" s="15"/>
+      <c r="AJ6">
+        <v>15</v>
+      </c>
+      <c r="AL6">
+        <v>3</v>
+      </c>
       <c r="AN6">
         <v>0</v>
       </c>
@@ -736,13 +850,15 @@
       </c>
       <c r="BX6" s="15"/>
     </row>
-    <row r="7" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:78">
+      <c r="AA7" s="21"/>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AH7">
         <v>1</v>
       </c>
+      <c r="AK7" s="8"/>
       <c r="AN7">
         <v>1</v>
       </c>
@@ -778,12 +894,18 @@
       </c>
       <c r="BX7" s="15"/>
     </row>
-    <row r="8" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:78">
       <c r="S8" s="13"/>
       <c r="T8" s="12"/>
       <c r="U8" s="3"/>
       <c r="V8" s="12"/>
       <c r="W8" s="14"/>
+      <c r="Z8">
+        <v>19</v>
+      </c>
+      <c r="AB8">
+        <v>7</v>
+      </c>
       <c r="AC8">
         <v>2</v>
       </c>
@@ -797,6 +919,7 @@
       <c r="AI8">
         <v>5</v>
       </c>
+      <c r="AK8" s="21"/>
       <c r="AN8">
         <v>2</v>
       </c>
@@ -834,7 +957,7 @@
       <c r="BW8" s="12"/>
       <c r="BX8" s="16"/>
     </row>
-    <row r="9" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:78">
       <c r="U9" s="15"/>
       <c r="AE9">
         <v>3</v>
@@ -843,6 +966,12 @@
       <c r="AG9">
         <v>6</v>
       </c>
+      <c r="AJ9">
+        <v>14</v>
+      </c>
+      <c r="AL9">
+        <v>2</v>
+      </c>
       <c r="AN9">
         <v>3</v>
       </c>
@@ -877,9 +1006,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:78" ht="15" thickBot="1">
       <c r="U10" s="15"/>
+      <c r="Y10">
+        <v>18</v>
+      </c>
+      <c r="AA10">
+        <v>6</v>
+      </c>
       <c r="AF10" s="1"/>
+      <c r="AJ10">
+        <v>18</v>
+      </c>
+      <c r="AL10">
+        <v>6</v>
+      </c>
       <c r="AN10">
         <v>4</v>
       </c>
@@ -914,12 +1055,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:78">
       <c r="U11" s="15"/>
+      <c r="Z11" s="22"/>
       <c r="AE11">
         <v>7</v>
       </c>
       <c r="AF11" s="8"/>
+      <c r="AK11" s="8"/>
       <c r="AN11">
         <v>5</v>
       </c>
@@ -954,10 +1097,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:78">
       <c r="S12" s="17"/>
       <c r="T12" s="12"/>
       <c r="U12" s="16"/>
+      <c r="Z12" s="23"/>
       <c r="AC12">
         <v>11</v>
       </c>
@@ -967,6 +1111,7 @@
       <c r="AG12">
         <v>8</v>
       </c>
+      <c r="AK12" s="21"/>
       <c r="AN12">
         <v>6</v>
       </c>
@@ -1001,13 +1146,23 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:78" ht="15" thickBot="1">
+      <c r="Z13" s="24"/>
+      <c r="AA13">
+        <v>8</v>
+      </c>
       <c r="AD13">
         <v>10</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
+      <c r="AJ13">
+        <v>17</v>
+      </c>
+      <c r="AL13">
+        <v>5</v>
+      </c>
       <c r="AN13">
         <v>7</v>
       </c>
@@ -1030,7 +1185,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:78">
+      <c r="Y14">
+        <v>20</v>
+      </c>
       <c r="AN14">
         <v>8</v>
       </c>
@@ -1056,7 +1214,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:78">
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>5</v>
+      </c>
       <c r="AN15">
         <v>9</v>
       </c>
@@ -1091,7 +1261,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:78" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:78">
+      <c r="AE16" s="1"/>
+      <c r="AI16" s="1"/>
       <c r="AN16">
         <v>10</v>
       </c>
@@ -1126,7 +1298,25 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="17" spans="26:61">
+      <c r="Z17">
+        <v>22</v>
+      </c>
+      <c r="AB17">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>12</v>
+      </c>
+      <c r="AF17">
+        <v>14</v>
+      </c>
+      <c r="AH17">
+        <v>13</v>
+      </c>
+      <c r="AJ17">
+        <v>17</v>
+      </c>
       <c r="AN17">
         <v>11</v>
       </c>
@@ -1161,7 +1351,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="18" spans="26:61">
+      <c r="AA18" s="1"/>
       <c r="AV18">
         <v>12</v>
       </c>
@@ -1187,7 +1378,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="19" spans="26:61">
+      <c r="Z19">
+        <v>23</v>
+      </c>
+      <c r="AB19">
+        <v>11</v>
+      </c>
+      <c r="AE19">
+        <v>23</v>
+      </c>
+      <c r="AH19">
+        <v>19</v>
+      </c>
       <c r="AV19">
         <v>13</v>
       </c>
@@ -1213,7 +1416,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="20" spans="26:61">
+      <c r="Z20">
+        <v>21</v>
+      </c>
+      <c r="AB20">
+        <v>9</v>
+      </c>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="4"/>
       <c r="AV20">
         <v>14</v>
       </c>
@@ -1239,7 +1450,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="21" spans="26:61">
+      <c r="AA21" s="1"/>
+      <c r="AE21">
+        <v>11</v>
+      </c>
+      <c r="AH21">
+        <v>7</v>
+      </c>
       <c r="AV21">
         <v>15</v>
       </c>
@@ -1253,7 +1471,13 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="22" spans="26:61">
+      <c r="Z22">
+        <v>20</v>
+      </c>
+      <c r="AB22">
+        <v>8</v>
+      </c>
       <c r="AV22">
         <v>16</v>
       </c>
@@ -1267,7 +1491,13 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="23" spans="26:61">
+      <c r="AD23">
+        <v>21</v>
+      </c>
+      <c r="AF23">
+        <v>9</v>
+      </c>
       <c r="AV23">
         <v>17</v>
       </c>
@@ -1281,7 +1511,8 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="24" spans="26:61">
+      <c r="AE24" s="1"/>
       <c r="AV24">
         <v>18</v>
       </c>
@@ -1295,7 +1526,13 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="25" spans="26:61">
+      <c r="AD25">
+        <v>22</v>
+      </c>
+      <c r="AF25">
+        <v>10</v>
+      </c>
       <c r="AV25">
         <v>19</v>
       </c>
@@ -1309,7 +1546,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="26" spans="26:61">
       <c r="AV26">
         <v>20</v>
       </c>
@@ -1323,7 +1560,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="27" spans="26:61">
       <c r="AV27">
         <v>21</v>
       </c>
@@ -1337,7 +1574,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="28" spans="26:61">
       <c r="AV28">
         <v>22</v>
       </c>
@@ -1351,7 +1588,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="40:61" x14ac:dyDescent="0.25">
+    <row r="29" spans="26:61">
       <c r="AV29">
         <v>23</v>
       </c>
